--- a/2022 data/excel_outputs/255_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/255_boothwise_data.xlsx
@@ -14,11 +14,83 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="499">
   <si>
     <t>AC 255 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -193,13 +265,16 @@
     <t>PRATHMIK KANYA PATHSHALA MAUAIMA BHAG</t>
   </si>
   <si>
-    <t>PRATHMIK KANYA PATHSHALA MAUAIMA BHAG-■</t>
+    <t>JILA PARISHAD PRARIMARI PATHASHALA KHANAPUR UTTARI BHAG-1</t>
+  </si>
+  <si>
+    <t>JILA PARISHAD PRARIMARI PATHASHALA KHANAPUR UTTARI BHAG-2</t>
   </si>
   <si>
     <t>STANDARD INTERMIDIATE COLLEGE MAUAIMA UTTARI BHAG</t>
   </si>
   <si>
-    <t>STANDARD INTERMIDIATE COLLEGE MAUAIMA UTTARI BHAG-■</t>
+    <t>JILA PARISHAD PRAIMARI PATHASHALA MAUDOSTAPUR</t>
   </si>
   <si>
     <t>STANDARD INTERMIDIATE COLLEGE MAUAIMA UTTARI MADYA BHAG-1</t>
@@ -1442,8 +1517,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1459,7 +1542,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1467,12 +1550,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1771,85 +1872,157 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="D2" t="s">
-        <v>452</v>
+        <v>477</v>
       </c>
       <c r="E2" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="F2" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="G2" t="s">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="H2" t="s">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="I2" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="J2" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="K2" t="s">
-        <v>459</v>
+        <v>484</v>
       </c>
       <c r="L2" t="s">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="M2" t="s">
-        <v>461</v>
+        <v>486</v>
       </c>
       <c r="N2" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="O2" t="s">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="P2" t="s">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="Q2" t="s">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="R2" t="s">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="S2" t="s">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="T2" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="U2" t="s">
-        <v>469</v>
+        <v>494</v>
       </c>
       <c r="V2" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="W2" t="s">
-        <v>471</v>
+        <v>496</v>
       </c>
       <c r="X2" t="s">
-        <v>472</v>
+        <v>497</v>
       </c>
       <c r="Y2" t="s">
-        <v>473</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1857,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>965</v>
@@ -1934,7 +2107,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>954</v>
@@ -2011,7 +2184,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>874</v>
@@ -2088,7 +2261,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>1032</v>
@@ -2165,7 +2338,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>982</v>
@@ -2242,7 +2415,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>947</v>
@@ -2319,7 +2492,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>713</v>
@@ -2396,7 +2569,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>1089</v>
@@ -2473,7 +2646,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>630</v>
@@ -2550,7 +2723,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>1118</v>
@@ -2627,7 +2800,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>623</v>
@@ -2704,7 +2877,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C14">
         <v>893</v>
@@ -2781,7 +2954,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>955</v>
@@ -2858,7 +3031,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C16">
         <v>951</v>
@@ -2935,7 +3108,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C17">
         <v>1060</v>
@@ -3012,7 +3185,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C18">
         <v>1011</v>
@@ -3089,7 +3262,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C19">
         <v>542</v>
@@ -3166,7 +3339,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C20">
         <v>912</v>
@@ -3243,7 +3416,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C21">
         <v>838</v>
@@ -3320,7 +3493,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="C22">
         <v>848</v>
@@ -3397,7 +3570,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C23">
         <v>631</v>
@@ -3474,7 +3647,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C24">
         <v>704</v>
@@ -3551,7 +3724,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C25">
         <v>664</v>
@@ -3628,7 +3801,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C26">
         <v>960</v>
@@ -3705,7 +3878,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C27">
         <v>709</v>
@@ -3782,7 +3955,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C28">
         <v>775</v>
@@ -3859,7 +4032,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="C29">
         <v>735</v>
@@ -3936,7 +4109,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C30">
         <v>1140</v>
@@ -4013,7 +4186,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C31">
         <v>617</v>
@@ -4090,7 +4263,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C32">
         <v>659</v>
@@ -4167,7 +4340,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C33">
         <v>1009</v>
@@ -4244,7 +4417,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C34">
         <v>1077</v>
@@ -4321,7 +4494,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C35">
         <v>1038</v>
@@ -4398,7 +4571,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C36">
         <v>1002</v>
@@ -4475,7 +4648,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C37">
         <v>1029</v>
@@ -4552,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="C38">
         <v>1002</v>
@@ -4629,7 +4802,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="C39">
         <v>938</v>
@@ -4706,7 +4879,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="C40">
         <v>935</v>
@@ -4783,7 +4956,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C41">
         <v>1008</v>
@@ -4860,7 +5033,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C42">
         <v>906</v>
@@ -4937,7 +5110,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="C43">
         <v>878</v>
@@ -5014,7 +5187,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C44">
         <v>886</v>
@@ -5091,7 +5264,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C45">
         <v>891</v>
@@ -5168,7 +5341,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C46">
         <v>611</v>
@@ -5245,7 +5418,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="C47">
         <v>592</v>
@@ -5322,7 +5495,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C48">
         <v>910</v>
@@ -5399,7 +5572,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C49">
         <v>903</v>
@@ -5476,7 +5649,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="C50">
         <v>825</v>
@@ -5553,7 +5726,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="C51">
         <v>668</v>
@@ -5630,7 +5803,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C52">
         <v>1124</v>
@@ -5707,7 +5880,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C53">
         <v>898</v>
@@ -5784,7 +5957,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C54">
         <v>755</v>
@@ -5861,7 +6034,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C55">
         <v>704</v>
@@ -5938,7 +6111,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="C56">
         <v>1218</v>
@@ -6015,7 +6188,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="C57">
         <v>561</v>
@@ -6092,7 +6265,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C58">
         <v>790</v>
@@ -6169,7 +6342,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C59">
         <v>587</v>
@@ -6246,7 +6419,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C60">
         <v>992</v>
@@ -6323,7 +6496,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="C61">
         <v>960</v>
@@ -6400,7 +6573,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="C62">
         <v>700</v>
@@ -6477,7 +6650,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="C63">
         <v>1218</v>
@@ -6554,7 +6727,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="C64">
         <v>719</v>
@@ -6631,7 +6804,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C65">
         <v>998</v>
@@ -6708,7 +6881,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="C66">
         <v>615</v>
@@ -6785,7 +6958,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C67">
         <v>951</v>
@@ -6862,7 +7035,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C68">
         <v>851</v>
@@ -6939,7 +7112,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C69">
         <v>844</v>
@@ -7016,7 +7189,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="C70">
         <v>1012</v>
@@ -7093,7 +7266,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="C71">
         <v>1042</v>
@@ -7170,7 +7343,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="C72">
         <v>1036</v>
@@ -7247,7 +7420,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C73">
         <v>886</v>
@@ -7324,7 +7497,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="C74">
         <v>1000</v>
@@ -7401,7 +7574,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C75">
         <v>916</v>
@@ -7478,7 +7651,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C76">
         <v>633</v>
@@ -7555,7 +7728,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C77">
         <v>1184</v>
@@ -7632,7 +7805,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="C78">
         <v>546</v>
@@ -7709,7 +7882,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="C79">
         <v>998</v>
@@ -7786,7 +7959,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C80">
         <v>864</v>
@@ -7863,7 +8036,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="C81">
         <v>912</v>
@@ -7940,7 +8113,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="C82">
         <v>824</v>
@@ -8017,7 +8190,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="C83">
         <v>633</v>
@@ -8094,7 +8267,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="C84">
         <v>1024</v>
@@ -8171,7 +8344,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C85">
         <v>998</v>
@@ -8248,7 +8421,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="C86">
         <v>895</v>
@@ -8325,7 +8498,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="C87">
         <v>735</v>
@@ -8402,7 +8575,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="C88">
         <v>653</v>
@@ -8479,7 +8652,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="C89">
         <v>987</v>
@@ -8556,7 +8729,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C90">
         <v>780</v>
@@ -8633,7 +8806,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C91">
         <v>1199</v>
@@ -8710,7 +8883,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="C92">
         <v>1117</v>
@@ -8787,7 +8960,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="C93">
         <v>1221</v>
@@ -8864,7 +9037,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="C94">
         <v>1156</v>
@@ -8941,7 +9114,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="C95">
         <v>1148</v>
@@ -9018,7 +9191,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="C96">
         <v>1029</v>
@@ -9095,7 +9268,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="C97">
         <v>944</v>
@@ -9172,7 +9345,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="C98">
         <v>520</v>
@@ -9249,7 +9422,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C99">
         <v>903</v>
@@ -9326,7 +9499,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="C100">
         <v>922</v>
@@ -9403,7 +9576,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="C101">
         <v>827</v>
@@ -9480,7 +9653,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="C102">
         <v>692</v>
@@ -9557,7 +9730,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="C103">
         <v>662</v>
@@ -9634,7 +9807,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="C104">
         <v>662</v>
@@ -9711,7 +9884,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="C105">
         <v>702</v>
@@ -9788,7 +9961,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C106">
         <v>789</v>
@@ -9865,7 +10038,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="C107">
         <v>899</v>
@@ -9942,7 +10115,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="C108">
         <v>870</v>
@@ -10019,7 +10192,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="C109">
         <v>825</v>
@@ -10096,7 +10269,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="C110">
         <v>1076</v>
@@ -10173,7 +10346,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="C111">
         <v>1059</v>
@@ -10250,7 +10423,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="C112">
         <v>857</v>
@@ -10327,7 +10500,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="C113">
         <v>737</v>
@@ -10404,7 +10577,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="C114">
         <v>818</v>
@@ -10481,7 +10654,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="C115">
         <v>879</v>
@@ -10558,7 +10731,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="C116">
         <v>890</v>
@@ -10635,7 +10808,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="C117">
         <v>836</v>
@@ -10712,7 +10885,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="C118">
         <v>1021</v>
@@ -10789,7 +10962,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="C119">
         <v>764</v>
@@ -10866,7 +11039,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="C120">
         <v>626</v>
@@ -10943,7 +11116,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C121">
         <v>601</v>
@@ -11020,7 +11193,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="C122">
         <v>908</v>
@@ -11097,7 +11270,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="C123">
         <v>1024</v>
@@ -11174,7 +11347,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="C124">
         <v>682</v>
@@ -11251,7 +11424,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C125">
         <v>708</v>
@@ -11328,7 +11501,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C126">
         <v>907</v>
@@ -11405,7 +11578,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="C127">
         <v>407</v>
@@ -11482,7 +11655,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="C128">
         <v>1199</v>
@@ -11559,7 +11732,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="C129">
         <v>639</v>
@@ -11636,7 +11809,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C130">
         <v>608</v>
@@ -11713,7 +11886,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="C131">
         <v>621</v>
@@ -11790,7 +11963,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="C132">
         <v>658</v>
@@ -11867,7 +12040,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="C133">
         <v>1048</v>
@@ -11944,7 +12117,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="C134">
         <v>617</v>
@@ -12021,7 +12194,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="C135">
         <v>766</v>
@@ -12098,7 +12271,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="C136">
         <v>834</v>
@@ -12175,7 +12348,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="C137">
         <v>593</v>
@@ -12252,7 +12425,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C138">
         <v>642</v>
@@ -12329,7 +12502,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C139">
         <v>657</v>
@@ -12406,7 +12579,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="C140">
         <v>501</v>
@@ -12483,7 +12656,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C141">
         <v>1064</v>
@@ -12560,7 +12733,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="C142">
         <v>818</v>
@@ -12637,7 +12810,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="C143">
         <v>908</v>
@@ -12714,7 +12887,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="C144">
         <v>722</v>
@@ -12791,7 +12964,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="C145">
         <v>692</v>
@@ -12868,7 +13041,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="C146">
         <v>542</v>
@@ -12945,7 +13118,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="C147">
         <v>548</v>
@@ -13022,7 +13195,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="C148">
         <v>750</v>
@@ -13099,7 +13272,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="C149">
         <v>1185</v>
@@ -13176,7 +13349,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="C150">
         <v>732</v>
@@ -13253,7 +13426,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="C151">
         <v>715</v>
@@ -13330,7 +13503,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="C152">
         <v>1220</v>
@@ -13407,7 +13580,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C153">
         <v>1059</v>
@@ -13484,7 +13657,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="C154">
         <v>948</v>
@@ -13561,7 +13734,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="C155">
         <v>698</v>
@@ -13638,7 +13811,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="C156">
         <v>887</v>
@@ -13715,7 +13888,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="C157">
         <v>497</v>
@@ -13792,7 +13965,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C158">
         <v>1061</v>
@@ -13869,7 +14042,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="C159">
         <v>871</v>
@@ -13946,7 +14119,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="C160">
         <v>1198</v>
@@ -14023,7 +14196,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="C161">
         <v>1044</v>
@@ -14100,7 +14273,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="C162">
         <v>956</v>
@@ -14177,7 +14350,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="C163">
         <v>998</v>
@@ -14254,7 +14427,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="C164">
         <v>588</v>
@@ -14331,7 +14504,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="C165">
         <v>747</v>
@@ -14408,7 +14581,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C166">
         <v>742</v>
@@ -14485,7 +14658,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C167">
         <v>999</v>
@@ -14562,7 +14735,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="C168">
         <v>552</v>
@@ -14639,7 +14812,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="C169">
         <v>1189</v>
@@ -14716,7 +14889,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="C170">
         <v>712</v>
@@ -14793,7 +14966,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="C171">
         <v>648</v>
@@ -14870,7 +15043,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="C172">
         <v>662</v>
@@ -14947,7 +15120,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="C173">
         <v>560</v>
@@ -15024,7 +15197,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="C174">
         <v>1091</v>
@@ -15101,7 +15274,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="C175">
         <v>1169</v>
@@ -15178,7 +15351,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="C176">
         <v>672</v>
@@ -15255,7 +15428,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="C177">
         <v>697</v>
@@ -15332,7 +15505,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="C178">
         <v>486</v>
@@ -15409,7 +15582,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="C179">
         <v>787</v>
@@ -15486,7 +15659,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="C180">
         <v>720</v>
@@ -15563,7 +15736,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="C181">
         <v>1139</v>
@@ -15640,7 +15813,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="C182">
         <v>577</v>
@@ -15717,7 +15890,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="C183">
         <v>828</v>
@@ -15794,7 +15967,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="C184">
         <v>842</v>
@@ -15871,7 +16044,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="C185">
         <v>1211</v>
@@ -15948,7 +16121,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="C186">
         <v>674</v>
@@ -16025,7 +16198,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="C187">
         <v>1050</v>
@@ -16102,7 +16275,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="C188">
         <v>1040</v>
@@ -16179,7 +16352,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="C189">
         <v>893</v>
@@ -16256,7 +16429,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="C190">
         <v>794</v>
@@ -16333,7 +16506,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="C191">
         <v>765</v>
@@ -16410,7 +16583,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="C192">
         <v>760</v>
@@ -16487,7 +16660,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="C193">
         <v>1217</v>
@@ -16564,7 +16737,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C194">
         <v>971</v>
@@ -16641,7 +16814,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="C195">
         <v>793</v>
@@ -16718,7 +16891,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="C196">
         <v>790</v>
@@ -16795,7 +16968,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="C197">
         <v>824</v>
@@ -16872,7 +17045,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="C198">
         <v>855</v>
@@ -16949,7 +17122,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="C199">
         <v>844</v>
@@ -17026,7 +17199,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="C200">
         <v>1102</v>
@@ -17103,7 +17276,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="C201">
         <v>963</v>
@@ -17180,7 +17353,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="C202">
         <v>1052</v>
@@ -17257,7 +17430,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="C203">
         <v>1112</v>
@@ -17334,7 +17507,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="C204">
         <v>1087</v>
@@ -17411,7 +17584,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="C205">
         <v>943</v>
@@ -17488,7 +17661,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="C206">
         <v>1014</v>
@@ -17565,7 +17738,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="C207">
         <v>1053</v>
@@ -17642,7 +17815,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="C208">
         <v>733</v>
@@ -17719,7 +17892,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="C209">
         <v>662</v>
@@ -17796,7 +17969,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="C210">
         <v>748</v>
@@ -17873,7 +18046,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="C211">
         <v>715</v>
@@ -17950,7 +18123,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="C212">
         <v>945</v>
@@ -18027,7 +18200,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="C213">
         <v>339</v>
@@ -18104,7 +18277,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="C214">
         <v>907</v>
@@ -18181,7 +18354,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="C215">
         <v>872</v>
@@ -18258,7 +18431,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C216">
         <v>950</v>
@@ -18335,7 +18508,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="C217">
         <v>1139</v>
@@ -18412,7 +18585,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="C218">
         <v>1142</v>
@@ -18489,7 +18662,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="C219">
         <v>1058</v>
@@ -18566,7 +18739,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="C220">
         <v>826</v>
@@ -18643,7 +18816,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="C221">
         <v>697</v>
@@ -18720,7 +18893,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="C222">
         <v>979</v>
@@ -18797,7 +18970,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="C223">
         <v>828</v>
@@ -18874,7 +19047,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="C224">
         <v>761</v>
@@ -18951,7 +19124,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="C225">
         <v>644</v>
@@ -19028,7 +19201,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="C226">
         <v>784</v>
@@ -19105,7 +19278,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="C227">
         <v>655</v>
@@ -19182,7 +19355,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="C228">
         <v>787</v>
@@ -19259,7 +19432,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="C229">
         <v>1038</v>
@@ -19336,7 +19509,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="C230">
         <v>1051</v>
@@ -19413,7 +19586,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="C231">
         <v>779</v>
@@ -19490,7 +19663,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="C232">
         <v>903</v>
@@ -19567,7 +19740,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="C233">
         <v>610</v>
@@ -19644,7 +19817,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="C234">
         <v>905</v>
@@ -19721,7 +19894,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="C235">
         <v>645</v>
@@ -19798,7 +19971,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="C236">
         <v>615</v>
@@ -19875,7 +20048,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="C237">
         <v>927</v>
@@ -19952,7 +20125,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="C238">
         <v>1001</v>
@@ -20029,7 +20202,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="C239">
         <v>865</v>
@@ -20106,7 +20279,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="C240">
         <v>663</v>
@@ -20183,7 +20356,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="C241">
         <v>737</v>
@@ -20260,7 +20433,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="C242">
         <v>744</v>
@@ -20337,7 +20510,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="C243">
         <v>904</v>
@@ -20414,7 +20587,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C244">
         <v>799</v>
@@ -20491,7 +20664,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="C245">
         <v>608</v>
@@ -20568,7 +20741,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="C246">
         <v>825</v>
@@ -20645,7 +20818,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="C247">
         <v>900</v>
@@ -20722,7 +20895,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="C248">
         <v>1065</v>
@@ -20799,7 +20972,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="C249">
         <v>1167</v>
@@ -20876,7 +21049,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="C250">
         <v>998</v>
@@ -20953,7 +21126,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="C251">
         <v>946</v>
@@ -21030,7 +21203,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="C252">
         <v>1055</v>
@@ -21107,7 +21280,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="C253">
         <v>956</v>
@@ -21184,7 +21357,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="C254">
         <v>1116</v>
@@ -21261,7 +21434,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="C255">
         <v>1217</v>
@@ -21338,7 +21511,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="C256">
         <v>985</v>
@@ -21415,7 +21588,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="C257">
         <v>1239</v>
@@ -21492,7 +21665,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="C258">
         <v>1203</v>
@@ -21569,7 +21742,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="C259">
         <v>1194</v>
@@ -21646,7 +21819,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="C260">
         <v>462</v>
@@ -21723,7 +21896,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="C261">
         <v>1064</v>
@@ -21800,7 +21973,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="C262">
         <v>1112</v>
@@ -21877,7 +22050,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="C263">
         <v>900</v>
@@ -21954,7 +22127,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="C264">
         <v>907</v>
@@ -22031,7 +22204,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="C265">
         <v>672</v>
@@ -22108,7 +22281,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="C266">
         <v>890</v>
@@ -22185,7 +22358,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="C267">
         <v>1134</v>
@@ -22262,7 +22435,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="C268">
         <v>600</v>
@@ -22339,7 +22512,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="C269">
         <v>1104</v>
@@ -22416,7 +22589,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="C270">
         <v>605</v>
@@ -22493,7 +22666,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="C271">
         <v>650</v>
@@ -22570,7 +22743,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="C272">
         <v>835</v>
@@ -22647,7 +22820,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="C273">
         <v>826</v>
@@ -22724,7 +22897,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="C274">
         <v>472</v>
@@ -22801,7 +22974,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="C275">
         <v>599</v>
@@ -22878,7 +23051,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="C276">
         <v>639</v>
@@ -22955,7 +23128,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="C277">
         <v>738</v>
@@ -23032,7 +23205,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="C278">
         <v>609</v>
@@ -23109,7 +23282,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="C279">
         <v>971</v>
@@ -23186,7 +23359,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="C280">
         <v>539</v>
@@ -23263,7 +23436,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="C281">
         <v>909</v>
@@ -23340,7 +23513,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="C282">
         <v>1133</v>
@@ -23417,7 +23590,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="C283">
         <v>1148</v>
@@ -23494,7 +23667,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="C284">
         <v>1138</v>
@@ -23571,7 +23744,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="C285">
         <v>1162</v>
@@ -23648,7 +23821,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="C286">
         <v>914</v>
@@ -23725,7 +23898,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="C287">
         <v>1071</v>
@@ -23802,7 +23975,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="C288">
         <v>678</v>
@@ -23879,7 +24052,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="C289">
         <v>612</v>
@@ -23956,7 +24129,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="C290">
         <v>648</v>
@@ -24033,7 +24206,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="C291">
         <v>833</v>
@@ -24110,7 +24283,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C292">
         <v>781</v>
@@ -24187,7 +24360,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="C293">
         <v>637</v>
@@ -24264,7 +24437,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="C294">
         <v>1140</v>
@@ -24341,7 +24514,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="C295">
         <v>1137</v>
@@ -24418,7 +24591,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="C296">
         <v>634</v>
@@ -24495,7 +24668,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="C297">
         <v>800</v>
@@ -24572,7 +24745,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="C298">
         <v>1010</v>
@@ -24649,7 +24822,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="C299">
         <v>799</v>
@@ -24726,7 +24899,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="C300">
         <v>1041</v>
@@ -24803,7 +24976,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="C301">
         <v>670</v>
@@ -24880,7 +25053,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="C302">
         <v>675</v>
@@ -24957,7 +25130,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="C303">
         <v>796</v>
@@ -25034,7 +25207,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="C304">
         <v>770</v>
@@ -25111,7 +25284,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="C305">
         <v>515</v>
@@ -25188,7 +25361,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="C306">
         <v>833</v>
@@ -25265,7 +25438,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="C307">
         <v>568</v>
@@ -25342,7 +25515,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C308">
         <v>543</v>
@@ -25419,7 +25592,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="C309">
         <v>758</v>
@@ -25496,7 +25669,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="C310">
         <v>603</v>
@@ -25573,7 +25746,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="C311">
         <v>653</v>
@@ -25650,7 +25823,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="C312">
         <v>1058</v>
@@ -25727,7 +25900,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="C313">
         <v>817</v>
@@ -25804,7 +25977,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C314">
         <v>914</v>
@@ -25881,7 +26054,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="C315">
         <v>1101</v>
@@ -25958,7 +26131,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="C316">
         <v>990</v>
@@ -26035,7 +26208,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="C317">
         <v>596</v>
@@ -26112,7 +26285,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="C318">
         <v>774</v>
@@ -26189,7 +26362,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="C319">
         <v>871</v>
@@ -26266,7 +26439,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="C320">
         <v>610</v>
@@ -26343,7 +26516,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C321">
         <v>676</v>
@@ -26420,7 +26593,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="C322">
         <v>772</v>
@@ -26497,7 +26670,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="C323">
         <v>611</v>
@@ -26574,7 +26747,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="C324">
         <v>1175</v>
@@ -26651,7 +26824,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C325">
         <v>1196</v>
@@ -26728,7 +26901,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="C326">
         <v>779</v>
@@ -26805,7 +26978,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C327">
         <v>1061</v>
@@ -26882,7 +27055,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C328">
         <v>1120</v>
@@ -26959,7 +27132,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="C329">
         <v>1115</v>
@@ -27036,7 +27209,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="C330">
         <v>1166</v>
@@ -27113,7 +27286,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="C331">
         <v>932</v>
@@ -27190,7 +27363,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C332">
         <v>1042</v>
@@ -27267,7 +27440,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="C333">
         <v>975</v>
@@ -27344,7 +27517,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="C334">
         <v>916</v>
@@ -27421,7 +27594,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="C335">
         <v>805</v>
@@ -27498,7 +27671,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>333</v>
+        <v>358</v>
       </c>
       <c r="C336">
         <v>501</v>
@@ -27575,7 +27748,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="C337">
         <v>593</v>
@@ -27652,7 +27825,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="C338">
         <v>1065</v>
@@ -27729,7 +27902,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="C339">
         <v>579</v>
@@ -27806,7 +27979,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="C340">
         <v>573</v>
@@ -27883,7 +28056,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="C341">
         <v>804</v>
@@ -27960,7 +28133,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="C342">
         <v>1139</v>
@@ -28037,7 +28210,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="C343">
         <v>660</v>
@@ -28114,7 +28287,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="C344">
         <v>871</v>
@@ -28191,7 +28364,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="C345">
         <v>1072</v>
@@ -28268,7 +28441,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>343</v>
+        <v>368</v>
       </c>
       <c r="C346">
         <v>1045</v>
@@ -28345,7 +28518,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="C347">
         <v>512</v>
@@ -28422,7 +28595,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="C348">
         <v>601</v>
@@ -28499,7 +28672,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="C349">
         <v>621</v>
@@ -28576,7 +28749,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="C350">
         <v>838</v>
@@ -28653,7 +28826,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="C351">
         <v>744</v>
@@ -28730,7 +28903,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="C352">
         <v>640</v>
@@ -28807,7 +28980,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="C353">
         <v>707</v>
@@ -28884,7 +29057,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="C354">
         <v>1017</v>
@@ -28961,7 +29134,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="C355">
         <v>1033</v>
@@ -29038,7 +29211,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="C356">
         <v>906</v>
@@ -29115,7 +29288,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="C357">
         <v>754</v>
@@ -29192,7 +29365,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="C358">
         <v>921</v>
@@ -29269,7 +29442,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C359">
         <v>798</v>
@@ -29346,7 +29519,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="C360">
         <v>1040</v>
@@ -29423,7 +29596,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>358</v>
+        <v>383</v>
       </c>
       <c r="C361">
         <v>1100</v>
@@ -29500,7 +29673,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="C362">
         <v>643</v>
@@ -29577,7 +29750,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="C363">
         <v>653</v>
@@ -29654,7 +29827,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="C364">
         <v>767</v>
@@ -29731,7 +29904,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="C365">
         <v>711</v>
@@ -29808,7 +29981,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>363</v>
+        <v>388</v>
       </c>
       <c r="C366">
         <v>688</v>
@@ -29885,7 +30058,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="C367">
         <v>610</v>
@@ -29962,7 +30135,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="C368">
         <v>633</v>
@@ -30039,7 +30212,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="C369">
         <v>702</v>
@@ -30116,7 +30289,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="C370">
         <v>964</v>
@@ -30193,7 +30366,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="C371">
         <v>560</v>
@@ -30270,7 +30443,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="C372">
         <v>801</v>
@@ -30347,7 +30520,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="C373">
         <v>816</v>
@@ -30424,7 +30597,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C374">
         <v>863</v>
@@ -30501,7 +30674,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="C375">
         <v>777</v>
@@ -30578,7 +30751,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="C376">
         <v>841</v>
@@ -30655,7 +30828,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="C377">
         <v>846</v>
@@ -30732,7 +30905,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="C378">
         <v>765</v>
@@ -30809,7 +30982,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="C379">
         <v>1047</v>
@@ -30886,7 +31059,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="C380">
         <v>1036</v>
@@ -30963,7 +31136,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="C381">
         <v>1017</v>
@@ -31040,7 +31213,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="C382">
         <v>891</v>
@@ -31117,7 +31290,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="C383">
         <v>693</v>
@@ -31194,7 +31367,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="C384">
         <v>1216</v>
@@ -31271,7 +31444,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="C385">
         <v>1061</v>
@@ -31348,7 +31521,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="C386">
         <v>585</v>
@@ -31425,7 +31598,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="C387">
         <v>876</v>
@@ -31502,7 +31675,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="C388">
         <v>672</v>
@@ -31579,7 +31752,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="C389">
         <v>676</v>
@@ -31656,7 +31829,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="C390">
         <v>712</v>
@@ -31733,7 +31906,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="C391">
         <v>645</v>
@@ -31810,7 +31983,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="C392">
         <v>411</v>
@@ -31887,7 +32060,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="C393">
         <v>709</v>
@@ -31964,7 +32137,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="C394">
         <v>639</v>
@@ -32041,7 +32214,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="C395">
         <v>949</v>
@@ -32118,7 +32291,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>393</v>
+        <v>418</v>
       </c>
       <c r="C396">
         <v>447</v>
@@ -32195,7 +32368,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="C397">
         <v>987</v>
@@ -32272,7 +32445,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="C398">
         <v>1181</v>
@@ -32349,7 +32522,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="C399">
         <v>737</v>
@@ -32426,7 +32599,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="C400">
         <v>764</v>
@@ -32503,7 +32676,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>398</v>
+        <v>423</v>
       </c>
       <c r="C401">
         <v>808</v>
@@ -32580,7 +32753,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="C402">
         <v>1181</v>
@@ -32657,7 +32830,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="C403">
         <v>1089</v>
@@ -32734,7 +32907,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="C404">
         <v>1125</v>
@@ -32811,7 +32984,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C405">
         <v>759</v>
@@ -32888,7 +33061,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="C406">
         <v>852</v>
@@ -32965,7 +33138,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="C407">
         <v>616</v>
@@ -33042,7 +33215,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="C408">
         <v>608</v>
@@ -33119,7 +33292,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="C409">
         <v>621</v>
@@ -33196,7 +33369,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="C410">
         <v>657</v>
@@ -33273,7 +33446,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="C411">
         <v>637</v>
@@ -33350,7 +33523,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="C412">
         <v>592</v>
@@ -33427,7 +33600,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="C413">
         <v>942</v>
@@ -33504,7 +33677,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="C414">
         <v>524</v>
@@ -33581,7 +33754,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="C415">
         <v>729</v>
@@ -33658,7 +33831,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="C416">
         <v>688</v>
@@ -33735,7 +33908,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>414</v>
+        <v>439</v>
       </c>
       <c r="C417">
         <v>687</v>
@@ -33812,7 +33985,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="C418">
         <v>768</v>
@@ -33889,7 +34062,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="C419">
         <v>1200</v>
@@ -33966,7 +34139,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="C420">
         <v>600</v>
@@ -34043,7 +34216,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="C421">
         <v>697</v>
@@ -34120,7 +34293,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="C422">
         <v>978</v>
@@ -34197,7 +34370,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="C423">
         <v>743</v>
@@ -34274,7 +34447,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="C424">
         <v>774</v>
@@ -34351,7 +34524,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="C425">
         <v>736</v>
@@ -34428,7 +34601,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="C426">
         <v>958</v>
@@ -34505,7 +34678,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="C427">
         <v>497</v>
@@ -34582,7 +34755,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="C428">
         <v>1052</v>
@@ -34659,7 +34832,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="C429">
         <v>534</v>
@@ -34736,7 +34909,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="C430">
         <v>467</v>
@@ -34813,7 +34986,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="C431">
         <v>614</v>
@@ -34890,7 +35063,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="C432">
         <v>809</v>
@@ -34967,7 +35140,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="C433">
         <v>507</v>
@@ -35044,7 +35217,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
       <c r="C434">
         <v>710</v>
@@ -35121,7 +35294,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>432</v>
+        <v>457</v>
       </c>
       <c r="C435">
         <v>609</v>
@@ -35198,7 +35371,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="C436">
         <v>865</v>
@@ -35275,7 +35448,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>434</v>
+        <v>459</v>
       </c>
       <c r="C437">
         <v>1039</v>
@@ -35352,7 +35525,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="C438">
         <v>1006</v>
@@ -35429,7 +35602,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="C439">
         <v>912</v>
@@ -35506,7 +35679,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="C440">
         <v>712</v>
@@ -35583,7 +35756,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="C441">
         <v>400</v>
@@ -35660,7 +35833,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c r="C442">
         <v>1016</v>
@@ -35737,7 +35910,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="C443">
         <v>746</v>
@@ -35814,7 +35987,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>441</v>
+        <v>466</v>
       </c>
       <c r="C444">
         <v>620</v>
@@ -35891,7 +36064,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>442</v>
+        <v>467</v>
       </c>
       <c r="C445">
         <v>713</v>
@@ -35968,7 +36141,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>443</v>
+        <v>468</v>
       </c>
       <c r="C446">
         <v>711</v>
@@ -36045,7 +36218,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>444</v>
+        <v>469</v>
       </c>
       <c r="C447">
         <v>675</v>
@@ -36122,7 +36295,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="C448">
         <v>972</v>
@@ -36199,7 +36372,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="C449">
         <v>1155</v>
@@ -36276,7 +36449,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>447</v>
+        <v>472</v>
       </c>
       <c r="C450">
         <v>798</v>
@@ -36353,7 +36526,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>448</v>
+        <v>473</v>
       </c>
       <c r="C451">
         <v>880</v>
@@ -36430,7 +36603,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>449</v>
+        <v>474</v>
       </c>
       <c r="C452">
         <v>972</v>
@@ -36507,7 +36680,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="C453">
         <v>786</v>
